--- a/Colman_Ex3A_tables.xlsx
+++ b/Colman_Ex3A_tables.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isthe\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9A85C8-3B19-46E7-A864-AA412C6095A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16F6AFA-2CAB-45ED-8D55-2626096E8B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{50506C1E-2F79-4700-80F7-F28C74DA75DB}"/>
+    <workbookView xWindow="-16320" yWindow="-9450" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{50506C1E-2F79-4700-80F7-F28C74DA75DB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Customer" sheetId="1" r:id="rId1"/>
-    <sheet name="Dog" sheetId="2" r:id="rId2"/>
-    <sheet name="Employee" sheetId="3" r:id="rId3"/>
-    <sheet name="Walking_Schedule" sheetId="5" r:id="rId4"/>
-    <sheet name="Payment" sheetId="4" r:id="rId5"/>
+    <sheet name="customer" sheetId="1" r:id="rId1"/>
+    <sheet name="dog" sheetId="2" r:id="rId2"/>
+    <sheet name="employee" sheetId="3" r:id="rId3"/>
+    <sheet name="walking_schedule" sheetId="5" r:id="rId4"/>
+    <sheet name="payment" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t>employee_name</t>
   </si>
@@ -115,16 +115,81 @@
   </si>
   <si>
     <t>walk_status</t>
+  </si>
+  <si>
+    <t>Tiffany</t>
+  </si>
+  <si>
+    <t>385-222-2222</t>
+  </si>
+  <si>
+    <t>htiffany@fmail.com</t>
+  </si>
+  <si>
+    <t>2222 W 5555 S</t>
+  </si>
+  <si>
+    <t>Beni</t>
+  </si>
+  <si>
+    <t>Shih Tzu</t>
+  </si>
+  <si>
+    <t>Beni does not have any medical Problems</t>
+  </si>
+  <si>
+    <t>Beni gets anxious when around a lot of 
+dogs. He just needs time to settle in with all the dogs and he will be ok.</t>
+  </si>
+  <si>
+    <t>Netsa</t>
+  </si>
+  <si>
+    <t>510-111-1111</t>
+  </si>
+  <si>
+    <t>anetsa@fmail.com</t>
+  </si>
+  <si>
+    <t>888 W 9999 S</t>
+  </si>
+  <si>
+    <t>5:00pm</t>
+  </si>
+  <si>
+    <t>6:00pm</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>Debit Card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="166" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="168" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="169" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -159,15 +224,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -500,10 +574,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22998DEF-E11F-4727-BD72-036BEA282668}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -523,20 +600,40 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{324678E9-65E7-4932-A07B-6BE67CC2B670}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79ACD1BB-B6DA-41FF-8307-A98E786AC4BA}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="5" max="5" width="38.85546875" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -557,6 +654,26 @@
       </c>
       <c r="F1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -566,12 +683,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6AD5E0-537C-4CEF-8681-A235A6D30E79}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -591,20 +710,40 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{DFBBB5A6-DB67-4B8A-999E-335F8B2A98F5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F53DB6B-C1D2-42C0-B2A5-56D14D0BD028}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
     <col min="6" max="6" width="11.28515625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
@@ -633,6 +772,29 @@
         <v>23</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2">
+        <v>101</v>
+      </c>
+      <c r="C2">
+        <v>101</v>
+      </c>
+      <c r="D2" s="5">
+        <v>46318</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -640,13 +802,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21B74B32-5E7F-4210-9AA7-230358E7CB19}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="17.140625" customWidth="1"/>
   </cols>
@@ -671,6 +833,26 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2">
+        <v>101</v>
+      </c>
+      <c r="C2" s="5">
+        <v>46318</v>
+      </c>
+      <c r="D2" s="7">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
